--- a/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
@@ -139,7 +139,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -180,6 +180,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -570,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="10.2"/>
   <cols>
     <col width="12" customWidth="1" style="5" min="1" max="1"/>
@@ -614,7 +617,7 @@
     <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module Code</t>
+          <t>TC_001</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -622,10 +625,17 @@
           <t>TimKiem</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="2">
-        <f>"Fail: "&amp;COUNTIF(#REF!,"Fail")</f>
-        <v/>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Navigate to the homepage.
+Enter the keyword "Điện thoại" into the search box.
+Click the search button.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>The system displays a list of products whose titles or descriptions contain "Điện thoại". The results are sorted by relevance and each product shows its image, name, price, and availability status.</t>
+        </is>
       </c>
       <c r="E2" s="3">
         <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
@@ -640,7 +650,7 @@
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>TC_002</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -648,10 +658,17 @@
           <t>Lê Thị Ánh</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="2">
-        <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$973)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
-        <v/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Navigate to the homepage.
+Leave the search box blank.
+Click the search button.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>The system displays all products available in the store, paginated appropriately. A message "Showing all products" is visible above the list.</t>
+        </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
@@ -668,22 +685,24 @@
     <row r="4" ht="28.35" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>TC_003</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Test Case Description</t>
+          <t>Search with a keyword that yields no results (alternate flow 3a).</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Pre -Condition</t>
+          <t>Navigate to the homepage.
+Enter the keyword "Xe máy khổng lồ" into the search box.
+Click the search button.</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Test Case Procedure</t>
+          <t>The system displays the message: "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn." No product list is shown.</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -713,112 +732,109 @@
       </c>
     </row>
     <row r="5" customFormat="1" s="14">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>TC_001</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Verify that searching with a keyword returns matching products.</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>User is on the product search page.</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Step 1: Enter valid search input into the search field.
-Step 2: Press the search button.</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>The system displays a list of products that match the entered keyword.</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="n"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Search with a valid keyword</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>User is on the homepage</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Step 1: Enter a valid search keyword into the search field
+Step 2: Click the search button
+Step 3: Verify that a list of products matching the keyword is displayed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The search results page shows products whose titles or descriptions contain the entered keyword
+Each product entry displays an image, name, price and add-to-cart option</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>TC_002</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Verify that searching with an empty keyword shows all products.</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>User is on the product search page.</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Step 1: Leave the search field empty.
-Step 2: Press the search button.</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>The system displays the complete list of products available in the store.</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="n"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Search with no input (empty query)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>User is on the homepage</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Step 1: Leave the search field empty
+Step 2: Click the search button
+Step 3: Verify that all products in the store are displayed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>The product listing page shows the complete inventory of the store without any filtering
+No search result message is shown</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>22/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>TC_003</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Verify that searching with a non‑matching keyword shows an appropriate message.</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>User is on the product search page.</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Step 1: Enter an invalid or non‑matching search input into the search field.
-Step 2: Press the search button.</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>The system displays a message indicating that no products match the search criteria.</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="n"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Search with a keyword that yields no results</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>User is on the homepage</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Step 1: Enter an unlikely search keyword into the search field
+Step 2: Click the search button
+Step 3: Verify that a message indicating no products were found is displayed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>"No matching products were found for your selection." message appears prominently on the page
+The product list area remains empty or shows a placeholder image</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>22/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="8" customFormat="1" s="14"/>
     <row r="11" customFormat="1" s="14"/>

--- a/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
@@ -139,7 +139,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -185,6 +185,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="10.2"/>
   <cols>
     <col width="12" customWidth="1" style="5" min="1" max="1"/>
@@ -732,111 +736,127 @@
       </c>
     </row>
     <row r="5" customFormat="1" s="14">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>TC_001</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Search with a valid keyword</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>User is on the homepage</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Search with a valid keyword that returns products</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>User is on the home page</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>Step 1: Enter a valid search keyword into the search field
 Step 2: Click the search button
-Step 3: Verify that a list of products matching the keyword is displayed</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>The search results page shows products whose titles or descriptions contain the entered keyword
-Each product entry displays an image, name, price and add-to-cart option</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>22/03/2026</t>
-        </is>
-      </c>
+Step 3: Verify that a list of matching products is displayed</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>A product list appears with items that match the entered keyword</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="n"/>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>TC_002</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Search with no input (empty query)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>User is on the homepage</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Search with an empty keyword to view all products</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>User is on the home page</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Step 1: Leave the search field empty
 Step 2: Click the search button
-Step 3: Verify that all products in the store are displayed</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>The product listing page shows the complete inventory of the store without any filtering
-No search result message is shown</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>22/03/2026</t>
-        </is>
-      </c>
+Step 3: Verify that the full product catalog is displayed</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>The entire list of available products is shown on the page</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>TC_003</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Search with a keyword that yields no results</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>User is on the homepage</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Step 1: Enter an unlikely search keyword into the search field
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>User is on the home page</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Step 1: Enter an invalid or nonsensical search keyword into the search field
 Step 2: Click the search button
-Step 3: Verify that a message indicating no products were found is displayed</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>"No matching products were found for your selection." message appears prominently on the page
-The product list area remains empty or shows a placeholder image</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>22/03/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" customFormat="1" s="14"/>
+Step 3: Verify that a 'no results found' message is displayed</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>A notification appears stating no products match the search criteria</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="n"/>
+    </row>
+    <row r="8" customFormat="1" s="14">
+      <c r="A8" s="17" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n"/>
+      <c r="I8" s="18" t="n"/>
+    </row>
     <row r="11" customFormat="1" s="14"/>
   </sheetData>
   <hyperlinks>

--- a/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
@@ -30,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
@@ -75,12 +75,6 @@
       <family val="2"/>
       <b val="1"/>
       <color indexed="9"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
-      <family val="2"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -139,7 +133,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -182,13 +176,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="10.2"/>
   <cols>
     <col width="12" customWidth="1" style="5" min="1" max="1"/>
@@ -589,7 +576,8 @@
     <col width="12" customWidth="1" style="5" min="7" max="7"/>
     <col width="15" customWidth="1" style="5" min="8" max="8"/>
     <col width="25" customWidth="1" style="5" min="9" max="9"/>
-    <col width="9" customWidth="1" style="5" min="10" max="16384"/>
+    <col width="9" customWidth="1" style="5" min="10" max="10"/>
+    <col width="9" customWidth="1" style="5" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
@@ -621,7 +609,7 @@
     <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>TC_001</t>
+          <t>Module Code</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -629,17 +617,10 @@
           <t>TimKiem</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>Navigate to the homepage.
-Enter the keyword "Điện thoại" into the search box.
-Click the search button.</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>The system displays a list of products whose titles or descriptions contain "Điện thoại". The results are sorted by relevance and each product shows its image, name, price, and availability status.</t>
-        </is>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="2">
+        <f>"Fail: "&amp;COUNTIF(#REF!,"Fail")</f>
+        <v/>
       </c>
       <c r="E2" s="3">
         <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
@@ -654,7 +635,7 @@
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>TC_002</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -662,17 +643,10 @@
           <t>Lê Thị Ánh</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Navigate to the homepage.
-Leave the search box blank.
-Click the search button.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>The system displays all products available in the store, paginated appropriately. A message "Showing all products" is visible above the list.</t>
-        </is>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="2">
+        <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$973)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
+        <v/>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
@@ -689,24 +663,22 @@
     <row r="4" ht="28.35" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>TC_003</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Search with a keyword that yields no results (alternate flow 3a).</t>
+          <t>Test Case Description</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Navigate to the homepage.
-Enter the keyword "Xe máy khổng lồ" into the search box.
-Click the search button.</t>
+          <t>Pre -Condition</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>The system displays the message: "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn." No product list is shown.</t>
+          <t>Test Case Procedure</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -736,127 +708,117 @@
       </c>
     </row>
     <row r="5" customFormat="1" s="14">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>TC_001</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>Search with a valid keyword that returns products</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Search products with valid keyword</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>User is on the home page</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Step 1: Enter a valid search keyword into the search field
 Step 2: Click the search button
-Step 3: Verify that a list of matching products is displayed</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>A product list appears with items that match the entered keyword</t>
-        </is>
-      </c>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="18" t="n"/>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
-      <c r="I5" s="18" t="n"/>
+Step 3: Verify that the product list matching the keyword is displayed</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Product results relevant to the entered keyword are shown on the page</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>TC_002</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Search with an empty keyword to view all products</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Search products with empty keyword</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>User is on the home page</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Step 1: Leave the search field empty
 Step 2: Click the search button
-Step 3: Verify that the full product catalog is displayed</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>The entire list of available products is shown on the page</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="n"/>
-      <c r="G6" s="18" t="n"/>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="n"/>
+Step 3: Verify that all products in the store are displayed</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Full product catalog is shown after searching with an empty keyword</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>TC_003</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Search with a keyword that yields no results</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Search products with no matching results</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>User is on the home page</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Step 1: Enter an invalid or nonsensical search keyword into the search field
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Enter a search keyword that does not match any product into the search field
 Step 2: Click the search button
-Step 3: Verify that a 'no results found' message is displayed</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>A notification appears stating no products match the search criteria</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="n"/>
-    </row>
-    <row r="8" customFormat="1" s="14">
-      <c r="A8" s="17" t="n"/>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="18" t="n"/>
-      <c r="G8" s="18" t="n"/>
-      <c r="H8" s="18" t="n"/>
-      <c r="I8" s="18" t="n"/>
-    </row>
+Step 3: Verify that the message "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn." is displayed</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>A no‑results notification message appears on the page</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n"/>
+    </row>
+    <row r="8" customFormat="1" s="14"/>
     <row r="11" customFormat="1" s="14"/>
   </sheetData>
   <hyperlinks>
@@ -893,7 +855,8 @@
     <col width="9.6640625" customWidth="1" style="5" min="7" max="7"/>
     <col width="9" customWidth="1" style="5" min="8" max="8"/>
     <col width="17.21875" customWidth="1" style="5" min="9" max="9"/>
-    <col width="9" customWidth="1" style="5" min="10" max="16384"/>
+    <col width="9" customWidth="1" style="5" min="10" max="10"/>
+    <col width="9" customWidth="1" style="5" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
@@ -1186,7 +1149,8 @@
     <col width="9.6640625" customWidth="1" style="5" min="7" max="7"/>
     <col width="9" customWidth="1" style="5" min="8" max="8"/>
     <col width="17.21875" customWidth="1" style="5" min="9" max="9"/>
-    <col width="9" customWidth="1" style="5" min="10" max="16384"/>
+    <col width="9" customWidth="1" style="5" min="10" max="10"/>
+    <col width="9" customWidth="1" style="5" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
@@ -1457,7 +1421,8 @@
     <col width="9.6640625" customWidth="1" style="5" min="7" max="7"/>
     <col width="11.33203125" customWidth="1" style="5" min="8" max="8"/>
     <col width="17.21875" customWidth="1" style="5" min="9" max="9"/>
-    <col width="9" customWidth="1" style="5" min="10" max="16384"/>
+    <col width="9" customWidth="1" style="5" min="10" max="10"/>
+    <col width="9" customWidth="1" style="5" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.4" customHeight="1">

--- a/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
@@ -565,19 +565,19 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="10.2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
   <cols>
     <col width="12" customWidth="1" style="5" min="1" max="1"/>
     <col width="40" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
     <col width="30" customWidth="1" style="5" min="3" max="3"/>
     <col width="45" customWidth="1" style="5" min="4" max="4"/>
-    <col width="45" customWidth="1" style="5" min="5" max="6"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" style="5" min="7" max="7"/>
     <col width="15" customWidth="1" style="5" min="8" max="8"/>
     <col width="25" customWidth="1" style="5" min="9" max="9"/>
-    <col width="9" customWidth="1" style="5" min="10" max="10"/>
-    <col width="9" customWidth="1" style="5" min="11" max="16384"/>
+    <col width="9" customWidth="1" style="5" min="10" max="12"/>
+    <col width="9" customWidth="1" style="5" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
@@ -707,7 +707,7 @@
         </is>
       </c>
     </row>
-    <row r="5" customFormat="1" s="14">
+    <row r="5" ht="30.6" customFormat="1" customHeight="1" s="14">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>TC_001</t>
@@ -715,36 +715,38 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Search products with valid keyword</t>
+          <t>Search with a valid keyword that returns products</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>User is on the home page</t>
+          <t>User is on the homepage</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Enter a valid search keyword into the search field
+          <t>Step 1: Enter a valid search term into the search field
 Step 2: Click the search button
-Step 3: Verify that the product list matching the keyword is displayed</t>
+Step 3: Verify that a list of matching products is displayed</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Product results relevant to the entered keyword are shown on the page</t>
+          <t>The search results section contains at least one product card
+Each product card displays product name, image, and price
+The number of displayed products matches the expected count for the keyword</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="30.6" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>TC_002</t>
@@ -752,36 +754,38 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Search products with empty keyword</t>
+          <t>Search with an empty keyword to view all products</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>User is on the home page</t>
+          <t>User is on the homepage</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Step 1: Leave the search field empty
 Step 2: Click the search button
-Step 3: Verify that all products in the store are displayed</t>
+Step 3: Verify that the full product catalog is displayed</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Full product catalog is shown after searching with an empty keyword</t>
+          <t>The product listing page shows all available products
+No 'no results' message is displayed
+Pagination or infinite scroll functions correctly for the full list</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="40.8" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>TC_003</t>
@@ -789,37 +793,37 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Search products with no matching results</t>
+          <t>Search with a keyword that yields no matching products</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>User is on the home page</t>
+          <t>User is on the homepage</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Enter a search keyword that does not match any product into the search field
+          <t>Step 1: Enter an invalid or nonsensical search term into the search field
 Step 2: Click the search button
-Step 3: Verify that the message "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn." is displayed</t>
+Step 3: Verify that a 'no results' message is displayed</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>A no‑results notification message appears on the page</t>
+          <t>The system shows the message: "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn."
+No product cards are displayed in the search results area
+The search field retains the entered keyword for user reference</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
     </row>
-    <row r="8" customFormat="1" s="14"/>
-    <row r="11" customFormat="1" s="14"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="'Test report'!A1" display="Back to TestReport"/>
@@ -855,8 +859,8 @@
     <col width="9.6640625" customWidth="1" style="5" min="7" max="7"/>
     <col width="9" customWidth="1" style="5" min="8" max="8"/>
     <col width="17.21875" customWidth="1" style="5" min="9" max="9"/>
-    <col width="9" customWidth="1" style="5" min="10" max="10"/>
-    <col width="9" customWidth="1" style="5" min="11" max="16384"/>
+    <col width="9" customWidth="1" style="5" min="10" max="12"/>
+    <col width="9" customWidth="1" style="5" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
@@ -1149,8 +1153,8 @@
     <col width="9.6640625" customWidth="1" style="5" min="7" max="7"/>
     <col width="9" customWidth="1" style="5" min="8" max="8"/>
     <col width="17.21875" customWidth="1" style="5" min="9" max="9"/>
-    <col width="9" customWidth="1" style="5" min="10" max="10"/>
-    <col width="9" customWidth="1" style="5" min="11" max="16384"/>
+    <col width="9" customWidth="1" style="5" min="10" max="12"/>
+    <col width="9" customWidth="1" style="5" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
@@ -1421,8 +1425,8 @@
     <col width="9.6640625" customWidth="1" style="5" min="7" max="7"/>
     <col width="11.33203125" customWidth="1" style="5" min="8" max="8"/>
     <col width="17.21875" customWidth="1" style="5" min="9" max="9"/>
-    <col width="9" customWidth="1" style="5" min="10" max="10"/>
-    <col width="9" customWidth="1" style="5" min="11" max="16384"/>
+    <col width="9" customWidth="1" style="5" min="10" max="12"/>
+    <col width="9" customWidth="1" style="5" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.4" customHeight="1">

--- a/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
@@ -576,8 +576,8 @@
     <col width="12" customWidth="1" style="5" min="7" max="7"/>
     <col width="15" customWidth="1" style="5" min="8" max="8"/>
     <col width="25" customWidth="1" style="5" min="9" max="9"/>
-    <col width="9" customWidth="1" style="5" min="10" max="12"/>
-    <col width="9" customWidth="1" style="5" min="13" max="16384"/>
+    <col width="9" customWidth="1" style="5" min="10" max="16"/>
+    <col width="9" customWidth="1" style="5" min="17" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
@@ -707,7 +707,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30.6" customFormat="1" customHeight="1" s="14">
+    <row r="5" ht="60" customFormat="1" customHeight="1" s="14">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>TC_001</t>
@@ -715,38 +715,38 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Search with a valid keyword that returns products</t>
+          <t>Kiểm thử tìm kiếm sản phẩm với từ khóa hợp lệ</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>User is on the homepage</t>
+          <t>Người dùng đang ở trang chủ</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Enter a valid search term into the search field
-Step 2: Click the search button
-Step 3: Verify that a list of matching products is displayed</t>
+          <t>Step 1: Nhập từ khóa tìm kiếm vào ô tìm kiếm
+Step 2: Nhấn nút tìm kiếm
+Step 3: Kiểm tra danh sách sản phẩm hiển thị
+Step 4: Kiểm tra mỗi mục trong danh sách có chứa từ khóa đã nhập</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>The search results section contains at least one product card
-Each product card displays product name, image, and price
-The number of displayed products matches the expected count for the keyword</t>
+          <t>Sau khi nhấn nút, hệ thống xử lý yêu cầu và hiện ra danh sách các sản phẩm phù hợp
+Mỗi mục trên danh sách phải hiển thị tên, hình ảnh và giá của sản phẩm liên quan đến từ khóa</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
     </row>
-    <row r="6" ht="30.6" customHeight="1">
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>TC_002</t>
@@ -754,38 +754,36 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Search with an empty keyword to view all products</t>
+          <t>Kiểm thử tìm kiếm khi không nhập từ khóa</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>User is on the homepage</t>
+          <t>Người dùng đang ở trang chủ</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Leave the search field empty
-Step 2: Click the search button
-Step 3: Verify that the full product catalog is displayed</t>
+          <t>Step 1: Để trống ô tìm kiếm
+Step 2: Nhấn nút tìm kiếm
+Step 3: Kiểm tra danh sách sản phẩm hiển thị</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>The product listing page shows all available products
-No 'no results' message is displayed
-Pagination or infinite scroll functions correctly for the full list</t>
+          <t>Hệ thống hiển thị toàn bộ danh sách sản phẩm trong cửa hàng</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
     </row>
-    <row r="7" ht="40.8" customHeight="1">
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>TC_003</t>
@@ -793,33 +791,31 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Search with a keyword that yields no matching products</t>
+          <t>Kiểm thử tìm kiếm khi không có kết quả phù hợp</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>User is on the homepage</t>
+          <t>Người dùng đang ở trang chủ</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Enter an invalid or nonsensical search term into the search field
-Step 2: Click the search button
-Step 3: Verify that a 'no results' message is displayed</t>
+          <t>Step 1: Nhập từ khóa không tồn tại vào ô tìm kiếm
+Step 2: Nhấn nút tìm kiếm
+Step 3: Kiểm tra thông báo hiển thị</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>The system shows the message: "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn."
-No product cards are displayed in the search results area
-The search field retains the entered keyword for user reference</t>
+          <t>"Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn."</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
@@ -859,8 +855,8 @@
     <col width="9.6640625" customWidth="1" style="5" min="7" max="7"/>
     <col width="9" customWidth="1" style="5" min="8" max="8"/>
     <col width="17.21875" customWidth="1" style="5" min="9" max="9"/>
-    <col width="9" customWidth="1" style="5" min="10" max="12"/>
-    <col width="9" customWidth="1" style="5" min="13" max="16384"/>
+    <col width="9" customWidth="1" style="5" min="10" max="16"/>
+    <col width="9" customWidth="1" style="5" min="17" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
@@ -1153,8 +1149,8 @@
     <col width="9.6640625" customWidth="1" style="5" min="7" max="7"/>
     <col width="9" customWidth="1" style="5" min="8" max="8"/>
     <col width="17.21875" customWidth="1" style="5" min="9" max="9"/>
-    <col width="9" customWidth="1" style="5" min="10" max="12"/>
-    <col width="9" customWidth="1" style="5" min="13" max="16384"/>
+    <col width="9" customWidth="1" style="5" min="10" max="16"/>
+    <col width="9" customWidth="1" style="5" min="17" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
@@ -1414,22 +1410,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="10.2"/>
   <cols>
     <col width="14.33203125" customWidth="1" style="5" min="1" max="1"/>
     <col width="18.5546875" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-    <col width="27.6640625" customWidth="1" style="5" min="3" max="3"/>
-    <col width="43.6640625" customWidth="1" style="5" min="4" max="4"/>
-    <col width="40.44140625" customWidth="1" style="5" min="5" max="6"/>
+    <col width="22.109375" customWidth="1" style="5" min="3" max="3"/>
+    <col width="40.33203125" customWidth="1" style="5" min="4" max="4"/>
+    <col width="30.33203125" customWidth="1" style="5" min="5" max="6"/>
     <col width="9.6640625" customWidth="1" style="5" min="7" max="7"/>
-    <col width="11.33203125" customWidth="1" style="5" min="8" max="8"/>
+    <col width="9" customWidth="1" style="5" min="8" max="8"/>
     <col width="17.21875" customWidth="1" style="5" min="9" max="9"/>
-    <col width="9" customWidth="1" style="5" min="10" max="12"/>
-    <col width="9" customWidth="1" style="5" min="13" max="16384"/>
+    <col width="9" customWidth="1" style="5" min="10" max="16"/>
+    <col width="9" customWidth="1" style="5" min="17" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.4" customHeight="1">
+    <row r="1" ht="12.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Back to TestReport</t>
@@ -1455,7 +1451,7 @@
       </c>
       <c r="G1" s="4" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Module Code</t>
@@ -1477,7 +1473,7 @@
       </c>
       <c r="G2" s="4" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Tester</t>
@@ -1490,20 +1486,20 @@
       </c>
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="2">
-        <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$973)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
+        <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$971)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
         <v/>
       </c>
       <c r="E3" s="8">
-        <f>"Number of cases: "&amp;(COUNTA($A$5:$A$973))</f>
+        <f>"Number of cases: "&amp;(COUNTA($A$5:$A$971))</f>
         <v/>
       </c>
       <c r="F3" s="8">
-        <f>"Number of cases: "&amp;(COUNTA($A$5:$A$973))</f>
+        <f>"Number of cases: "&amp;(COUNTA($A$5:$A$971))</f>
         <v/>
       </c>
       <c r="G3" s="9" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="28.35" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1605,7 +1601,7 @@
       <c r="H9" s="13" t="n"/>
       <c r="I9" s="11" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" customFormat="1" s="14">
       <c r="A10" s="11" t="n"/>
       <c r="B10" s="12" t="n"/>
       <c r="C10" s="15" t="n"/>
@@ -1616,7 +1612,7 @@
       <c r="H10" s="13" t="n"/>
       <c r="I10" s="11" t="n"/>
     </row>
-    <row r="11" customFormat="1" s="14">
+    <row r="11">
       <c r="A11" s="11" t="n"/>
       <c r="B11" s="12" t="n"/>
       <c r="C11" s="15" t="n"/>
@@ -1671,149 +1667,6 @@
       <c r="H15" s="13" t="n"/>
       <c r="I15" s="11" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="11" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="11" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="11" t="n"/>
-    </row>
-    <row r="19" customFormat="1" s="14">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="11" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="11" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="11" t="n"/>
-    </row>
-    <row r="22" customFormat="1" s="14">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="11" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="11" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="11" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="15" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="11" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="11" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="15" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="11" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="11" t="n"/>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="'Test report'!A1" display="Back to TestReport"/>

--- a/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
@@ -707,7 +707,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customFormat="1" customHeight="1" s="14">
+    <row r="5" ht="45" customFormat="1" customHeight="1" s="14">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>TC_001</t>
@@ -715,7 +715,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Kiểm thử tìm kiếm sản phẩm với từ khóa hợp lệ</t>
+          <t>Tìm kiếm sản phẩm gấu bông với từ khóa hợp lệ</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -727,21 +727,19 @@
         <is>
           <t>Step 1: Nhập từ khóa tìm kiếm vào ô tìm kiếm
 Step 2: Nhấn nút tìm kiếm
-Step 3: Kiểm tra danh sách sản phẩm hiển thị
-Step 4: Kiểm tra mỗi mục trong danh sách có chứa từ khóa đã nhập</t>
+Step 3: Kiểm tra danh sách sản phẩm hiển thị</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Sau khi nhấn nút, hệ thống xử lý yêu cầu và hiện ra danh sách các sản phẩm phù hợp
-Mỗi mục trên danh sách phải hiển thị tên, hình ảnh và giá của sản phẩm liên quan đến từ khóa</t>
+          <t>Danh sách sản phẩm phù hợp với từ khóa được hiển thị trên giao diện</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
@@ -754,7 +752,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Kiểm thử tìm kiếm khi không nhập từ khóa</t>
+          <t>Tìm kiếm khi không nhập từ khóa</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -771,14 +769,14 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị toàn bộ danh sách sản phẩm trong cửa hàng</t>
+          <t>Tất cả danh sách sản phẩm trong cửa hàng được hiển thị trên giao diện</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
@@ -791,7 +789,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Kiểm thử tìm kiếm khi không có kết quả phù hợp</t>
+          <t>Tìm kiếm khi không có kết quả phù hợp</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -801,7 +799,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhập từ khóa không tồn tại vào ô tìm kiếm
+          <t>Step 1: Nhập từ khóa tìm kiếm vào ô tìm kiếm
 Step 2: Nhấn nút tìm kiếm
 Step 3: Kiểm tra thông báo hiển thị</t>
         </is>
@@ -815,11 +813,12 @@
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
     </row>
+    <row r="8" ht="45" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="'Test report'!A1" display="Back to TestReport"/>

--- a/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
@@ -715,31 +715,33 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Tìm kiếm sản phẩm gấu bông với từ khóa hợp lệ</t>
+          <t>Kiểm thử chức năng tìm kiếm sản phẩm gấu bông có từ khóa</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Người dùng đang ở trang chủ.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhập từ khóa tìm kiếm vào ô tìm kiếm
-Step 2: Nhấn nút tìm kiếm
-Step 3: Kiểm tra danh sách sản phẩm hiển thị</t>
+          <t>Step 1: Nhập từ khóa tìm kiếm vào ô tìm kiếm.
+Step 2: Nhấn nút tìm kiếm.
+Step 3: Kiểm tra danh sách sản phẩm phù hợp được hiển thị.</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Danh sách sản phẩm phù hợp với từ khóa được hiển thị trên giao diện</t>
+          <t>Khi nhập từ khóa, ô tìm kiếm chứa ký tự đã nhập.
+Sau khi nhấn nút tìm kiếm, trang tải lại và chuyển sang chế độ kết quả.
+Danh sách sản phẩm hiển thị các mục có tên hoặc mô tả khớp với từ khóa.</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
@@ -752,31 +754,33 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Tìm kiếm khi không nhập từ khóa</t>
+          <t>Kiểm thử chức năng tìm kiếm khi không nhập bất kỳ từ khóa nào</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Người dùng đang ở trang chủ.</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Để trống ô tìm kiếm
-Step 2: Nhấn nút tìm kiếm
-Step 3: Kiểm tra danh sách sản phẩm hiển thị</t>
+          <t>Step 1: Để trống ô tìm kiếm (không nhập gì).
+Step 2: Nhấn nút tìm kiếm.
+Step 3: Kiểm tra rằng hệ thống hiển thị toàn bộ danh sách sản phẩm trong cửa hàng.</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Tất cả danh sách sản phẩm trong cửa hàng được hiển thị trên giao diện</t>
+          <t>Ô tìm kiếm không chứa ký tự nào.
+Sau khi nhấn nút tìm kiếm, trang tải lại và chuyển sang chế độ kết quả.
+Hiển thị danh sách đầy đủ tất cả các sản phẩm có sẵn trong cửa hàng.</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
@@ -789,31 +793,33 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Tìm kiếm khi không có kết quả phù hợp</t>
+          <t>Kiểm thử chức năng khi không tìm thấy sản phẩm phù hợp với từ khóa</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Người dùng đang ở trang chủ.</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhập từ khóa tìm kiếm vào ô tìm kiếm
-Step 2: Nhấn nút tìm kiếm
-Step 3: Kiểm tra thông báo hiển thị</t>
+          <t>Step 1: Nhập một từ khóa không tồn tại vào ô tìm kiếm.
+Step 2: Nhấn nút tìm kiếm.
+Step 3: Kiểm tra thông báo "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn.".</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>"Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn."</t>
+          <t>Ô tìm kiếm chứa từ khóa đã nhập.
+Sau khi nhấn nút tìm kiếm, trang tải lại và chuyển sang chế độ kết quả.
+Hiển thị thông báo "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn.".</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>

--- a/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TimKiem" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BinhLuan1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="BinhLuan" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="DatHangNhanh" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="MuaHang" sheetId="4" state="visible" r:id="rId4"/>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
   <cols>
     <col width="12" customWidth="1" style="5" min="1" max="1"/>
@@ -614,7 +614,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>TimKiem</t>
+          <t>BinhLuan</t>
         </is>
       </c>
       <c r="C2" s="7" t="n"/>
@@ -650,12 +650,12 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Number of cases: 3</t>
+          <t>Number of cases: 6</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>Number of cases: 3</t>
+          <t>Number of cases: 6</t>
         </is>
       </c>
       <c r="G3" s="9" t="n"/>
@@ -707,7 +707,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customFormat="1" customHeight="1" s="14">
+    <row r="5" ht="75" customFormat="1" customHeight="1" s="14">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>TC_001</t>
@@ -715,7 +715,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Kiểm thử chức năng tìm kiếm sản phẩm gấu bông có từ khóa</t>
+          <t>Thêm bình luận thành công</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -725,28 +725,28 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhập từ khóa tìm kiếm vào ô tìm kiếm.
-Step 2: Nhấn nút tìm kiếm.
-Step 3: Kiểm tra danh sách sản phẩm phù hợp được hiển thị.</t>
+          <t>Step 1: Nhấn vào liên kết chi tiết sản phẩm.
+Step 2: Nhập nội dung bình luận.
+Step 3: Nhập họ tên.
+Step 4: Nhập số điện thoại.
+Step 5: Nhấn nút "Gửi bình luận".</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Khi nhập từ khóa, ô tìm kiếm chứa ký tự đã nhập.
-Sau khi nhấn nút tìm kiếm, trang tải lại và chuyển sang chế độ kết quả.
-Danh sách sản phẩm hiển thị các mục có tên hoặc mô tả khớp với từ khóa.</t>
+          <t>Kiểm tra hiển thị thông báo "Gửi bình luận thành công."</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>TC_002</t>
@@ -754,38 +754,37 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Kiểm thử chức năng tìm kiếm khi không nhập bất kỳ từ khóa nào</t>
+          <t>Bình luận rỗng</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ.</t>
+          <t>Người dùng đang ở trang chi tiết sản phẩm.</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Để trống ô tìm kiếm (không nhập gì).
-Step 2: Nhấn nút tìm kiếm.
-Step 3: Kiểm tra rằng hệ thống hiển thị toàn bộ danh sách sản phẩm trong cửa hàng.</t>
+          <t>Step 1: Không nhập nội dung bình luận.
+Step 2: Nhập họ tên.
+Step 3: Nhập số điện thoại.
+Step 4: Nhấn nút "Gửi bình luận".</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Ô tìm kiếm không chứa ký tự nào.
-Sau khi nhấn nút tìm kiếm, trang tải lại và chuyển sang chế độ kết quả.
-Hiển thị danh sách đầy đủ tất cả các sản phẩm có sẵn trong cửa hàng.</t>
+          <t>Kiểm tra hiển thị thông báo "Bạn chưa nhập bình luận."</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>TC_003</t>
@@ -793,38 +792,150 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Kiểm thử chức năng khi không tìm thấy sản phẩm phù hợp với từ khóa</t>
+          <t>Họ tên rỗng</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ.</t>
+          <t>Người dùng đang ở trang chi tiết sản phẩm.</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhập một từ khóa không tồn tại vào ô tìm kiếm.
-Step 2: Nhấn nút tìm kiếm.
-Step 3: Kiểm tra thông báo "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn.".</t>
+          <t>Step 1: Nhập nội dung bình luận.
+Step 2: Không nhập họ tên.
+Step 3: Nhập số điện thoại.
+Step 4: Nhấn nút "Gửi bình luận".</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Ô tìm kiếm chứa từ khóa đã nhập.
-Sau khi nhấn nút tìm kiếm, trang tải lại và chuyển sang chế độ kết quả.
-Hiển thị thông báo "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn.".</t>
+          <t>Kiểm tra hiển thị thông báo "Bạn chưa nhập tên."</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
     </row>
-    <row r="8" ht="45" customHeight="1"/>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>TC_004</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Số điện thoại rỗng</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chi tiết sản phẩm.</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Nhập nội dung bình luận.
+Step 2: Nhập họ tên.
+Step 3: Không nhập số điện thoại.
+Step 4: Nhấn nút "Gửi bình luận".</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Kiểm tra hiển thị thông báo "Bạn chưa nhập số điện thoại."</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="12" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>TC_005</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Số điện thoại chứa ký tự không hợp lệ</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chi tiết sản phẩm.</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Nhập nội dung bình luận.
+Step 2: Nhập họ tên.
+Step 3: Nhập số điện thoại chứa ký tự không phải số.
+Step 4: Nhấn nút "Gửi bình luận".</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Kiểm tra hiển thị thông báo "Số điện thoại chỉ bao gồm những số."</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="12" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>TC_006</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Số điện thoại ít hơn 10 chữ số</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chi tiết sản phẩm.</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Nhập nội dung bình luận.
+Step 2: Nhập họ tên.
+Step 3: Nhập số điện thoại có ít hơn 10 chữ số.
+Step 4: Nhấn nút "Gửi bình luận".</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Kiểm tra hiển thị thông báo "Số điện thoại phải có ít nhất 10 số."</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr"/>
+      <c r="G10" s="12" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="'Test report'!A1" display="Back to TestReport"/>

--- a/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BinhLuan1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TimKiem" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="BinhLuan" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="DatHangNhanh" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="MuaHang" sheetId="4" state="visible" r:id="rId4"/>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
   <cols>
     <col width="12" customWidth="1" style="5" min="1" max="1"/>
@@ -614,7 +614,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>BinhLuan</t>
+          <t>TimKiem</t>
         </is>
       </c>
       <c r="C2" s="7" t="n"/>
@@ -650,12 +650,12 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Number of cases: 6</t>
+          <t>Number of cases: 3</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>Number of cases: 6</t>
+          <t>Number of cases: 3</t>
         </is>
       </c>
       <c r="G3" s="9" t="n"/>
@@ -707,7 +707,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="75" customFormat="1" customHeight="1" s="14">
+    <row r="5" ht="60" customFormat="1" customHeight="1" s="14">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>TC_001</t>
@@ -715,38 +715,39 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Thêm bình luận thành công</t>
+          <t>Tìm kiếm sản phẩm với từ khóa hợp lệ</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ.</t>
+          <t>Người dùng đang ở trang chủ</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhấn vào liên kết chi tiết sản phẩm.
-Step 2: Nhập nội dung bình luận.
-Step 3: Nhập họ tên.
-Step 4: Nhập số điện thoại.
-Step 5: Nhấn nút "Gửi bình luận".</t>
+          <t>Step 1: Nhập từ khóa tìm kiếm vào ô tìm kiếm
+Step 2: Nhấn nút "Tìm kiếm"
+Step 3: Kiểm tra danh sách sản phẩm hiển thị
+Step 4: Kiểm tra các chi tiết sản phẩm trong danh sách</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Kiểm tra hiển thị thông báo "Gửi bình luận thành công."</t>
+          <t>Hệ thống kiểm tra từ khóa tìm kiếm thành công
+Danh sách sản phẩm phù hợp với từ khóa được hiển thị
+Mỗi sản phẩm trong danh sách có thông tin đầy đủ và đúng dữ liệu</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>TC_002</t>
@@ -754,37 +755,36 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Bình luận rỗng</t>
+          <t>Tìm kiếm sản phẩm khi nhập không có từ khóa</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chi tiết sản phẩm.</t>
+          <t>Người dùng đang ở trang chủ</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Không nhập nội dung bình luận.
-Step 2: Nhập họ tên.
-Step 3: Nhập số điện thoại.
-Step 4: Nhấn nút "Gửi bình luận".</t>
+          <t>Step 1: Không nhập dữ liệu vào ô tìm kiếm
+Step 2: Nhấn nút "Tìm kiếm"
+Step 3: Kiểm tra danh sách sản phẩm hiển thị</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Kiểm tra hiển thị thông báo "Bạn chưa nhập bình luận."</t>
+          <t>Hệ thống hiển thị toàn bộ danh sách sản phẩm trong cửa hàng</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>TC_003</t>
@@ -792,150 +792,38 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Họ tên rỗng</t>
+          <t>Tìm kiếm sản phẩm khi không có kết quả phù hợp</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chi tiết sản phẩm.</t>
+          <t>Người dùng đang ở trang chủ</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhập nội dung bình luận.
-Step 2: Không nhập họ tên.
-Step 3: Nhập số điện thoại.
-Step 4: Nhấn nút "Gửi bình luận".</t>
+          <t>Step 1: Nhập từ khóa tìm kiếm không tồn tại vào ô tìm kiếm
+Step 2: Nhấn nút "Tìm kiếm"
+Step 3: Kiểm tra thông báo hiển thị</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Kiểm tra hiển thị thông báo "Bạn chưa nhập tên."</t>
+          <t>Hệ thống hiển thị thông báo "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn."</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>TC_004</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Số điện thoại rỗng</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Người dùng đang ở trang chi tiết sản phẩm.</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Step 1: Nhập nội dung bình luận.
-Step 2: Nhập họ tên.
-Step 3: Không nhập số điện thoại.
-Step 4: Nhấn nút "Gửi bình luận".</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Kiểm tra hiển thị thông báo "Bạn chưa nhập số điện thoại."</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="12" t="inlineStr"/>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr"/>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>TC_005</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Số điện thoại chứa ký tự không hợp lệ</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Người dùng đang ở trang chi tiết sản phẩm.</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Step 1: Nhập nội dung bình luận.
-Step 2: Nhập họ tên.
-Step 3: Nhập số điện thoại chứa ký tự không phải số.
-Step 4: Nhấn nút "Gửi bình luận".</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Kiểm tra hiển thị thông báo "Số điện thoại chỉ bao gồm những số."</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr"/>
-      <c r="G9" s="12" t="inlineStr"/>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="inlineStr"/>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>TC_006</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Số điện thoại ít hơn 10 chữ số</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Người dùng đang ở trang chi tiết sản phẩm.</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Step 1: Nhập nội dung bình luận.
-Step 2: Nhập họ tên.
-Step 3: Nhập số điện thoại có ít hơn 10 chữ số.
-Step 4: Nhấn nút "Gửi bình luận".</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Kiểm tra hiển thị thông báo "Số điện thoại phải có ít nhất 10 số."</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr"/>
-      <c r="G10" s="12" t="inlineStr"/>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr"/>
-    </row>
+    <row r="8" ht="60" customHeight="1"/>
+    <row r="9" ht="60" customHeight="1"/>
+    <row r="10" ht="60" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="'Test report'!A1" display="Back to TestReport"/>

--- a/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
@@ -7,9 +7,12 @@
   </bookViews>
   <sheets>
     <sheet name="TimKiem" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BinhLuan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="DatHangNhanh" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MuaHang" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
     <definedName name="ACTION">#REF!</definedName>
@@ -712,7 +715,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Kiểm thử tìm kiếm sản phẩm với từ khóa hợp lệ</t>
+          <t>Tìm kiếm sản phẩm với từ khóa hợp lệ</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -729,14 +732,14 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị danh sách các sản phẩm thỏa mãn từ khóa đã nhập.</t>
+          <t>Danh sách sản phẩm được hiển thị dựa trên từ khóa tìm kiếm</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
@@ -749,7 +752,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Kiểm thử tìm kiếm khi không nhập từ khóa</t>
+          <t>Tìm kiếm khi không nhập từ khóa</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -759,21 +762,21 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Không nhập bất kỳ ký tự nào vào ô tìm kiếm
+          <t>Step 1: Không nhập dữ liệu vào ô tìm kiếm
 Step 2: Nhấn nút "Tìm kiếm"
-Step 3: Kiểm tra kết quả hiển thị danh sách toàn bộ sản phẩm trong cửa hàng</t>
+Step 3: Kiểm tra kết quả hiển thị danh sách tất cả sản phẩm trong cửa hàng</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị tất cả các sản phẩm có sẵn trong kho.</t>
+          <t>Danh sách toàn bộ sản phẩm được hiển thị</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
@@ -786,7 +789,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Kiểm thử tìm kiếm khi không có sản phẩm phù hợp</t>
+          <t>Tìm kiếm khi không tìm thấy sản phẩm phù hợp</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -796,21 +799,21 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhập từ khóa không tồn tại vào ô tìm kiếm
+          <t>Step 1: Nhập từ khóa chưa tồn tại trong kho hàng vào ô tìm kiếm
 Step 2: Nhấn nút "Tìm kiếm"
-Step 3: Kiểm tra thông báo hiển thị khi không có sản phẩm nào khớp</t>
+Step 3: Kiểm tra thông báo hiển thị "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn."</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn."</t>
+          <t>"Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn." được hiển thị trên giao diện</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
@@ -834,4 +837,1118 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
+  <cols>
+    <col width="12" customWidth="1" style="5" min="1" max="1"/>
+    <col width="40" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
+    <col width="30" customWidth="1" style="5" min="3" max="3"/>
+    <col width="45" customWidth="1" style="5" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" style="5" min="7" max="7"/>
+    <col width="15" customWidth="1" style="5" min="8" max="8"/>
+    <col width="25" customWidth="1" style="5" min="9" max="9"/>
+    <col width="9" customWidth="1" style="5" min="10" max="17"/>
+    <col width="9" customWidth="1" style="5" min="18" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="12.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Back to TestReport</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>To Buglist</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="2">
+        <f>"Pass: "&amp;COUNTIF(#REF!,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E1" s="3">
+        <f>"Untested: "&amp;COUNTIF(#REF!,"Untest")</f>
+        <v/>
+      </c>
+      <c r="F1" s="3">
+        <f>"Untested: "&amp;COUNTIF(#REF!,"Untest")</f>
+        <v/>
+      </c>
+      <c r="G1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="12.75" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Module Code</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>BinhLuan</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="2">
+        <f>"Fail: "&amp;COUNTIF(#REF!,"Fail")</f>
+        <v/>
+      </c>
+      <c r="E2" s="3">
+        <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F2" s="3">
+        <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="12.75" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Lê Thị Ánh</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="2">
+        <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$973)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
+        <v/>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Number of cases: 6</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Number of cases: 6</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="n"/>
+    </row>
+    <row r="4" ht="28.35" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Test Case Description</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Pre -Condition</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Test Case Procedure</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Expected Output</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Actual Output</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Test date</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customFormat="1" customHeight="1" s="14">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Thêm bình luận thành công trên trang chi tiết sản phẩm</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Nhấn vào liên kết để điều hướng tới trang chi tiết sản phẩm
+Step 2: Nhập nội dung bình luận vào ô nhập
+Step 3: Nhập họ tên vào ô nhập
+Step 4: Nhập số điện thoại vào ô nhập
+Step 5: Nhấn nút "Gửi bình luận"
+Step 6: Kiểm tra thông báo hiển thị trên giao diện</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>"Gửi bình luận thành công." xuất hiện trên màn hình</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Không gửi được khi nội dung bình luận rỗng</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Nhấn vào liên kết để điều hướng tới trang chi tiết sản phẩm
+Step 2: Không nhập nội dung bình luận
+Step 3: Nhập họ tên vào ô nhập
+Step 4: Nhập số điện thoại vào ô nhập
+Step 5: Nhấn nút "Gửi bình luận"
+Step 6: Kiểm tra thông báo hiển thị trên giao diện</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>"Bạn chưa nhập bình luận." xuất hiện trên màn hình</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>TC_003</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Không gửi được khi họ tên rỗng</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Nhấn vào liên kết để điều hướng tới trang chi tiết sản phẩm
+Step 2: Nhập nội dung bình luận vào ô nhập
+Step 3: Không nhập họ tên
+Step 4: Nhập số điện thoại vào ô nhập
+Step 5: Nhấn nút "Gửi bình luận"
+Step 6: Kiểm tra thông báo hiển thị trên giao diện</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>"Bạn chưa nhập tên." xuất hiện trên màn hình</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n"/>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>TC_004</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Không gửi được khi số điện thoại rỗng</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Nhấn vào liên kết để điều hướng tới trang chi tiết sản phẩm
+Step 2: Nhập nội dung bình luận vào ô nhập
+Step 3: Nhập họ tên vào ô nhập
+Step 4: Không nhập số điện thoại
+Step 5: Nhấn nút "Gửi bình luận"
+Step 6: Kiểm tra thông báo hiển thị trên giao diện</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>"Bạn chưa nhập số điện thoại." xuất hiện trên màn hình</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="12" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>TC_005</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Không gửi được khi số điện thoại chứa ký tự không phải số</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Nhấn vào liên kết để điều hướng tới trang chi tiết sản phẩm
+Step 2: Nhập nội dung bình luận vào ô nhập
+Step 3: Nhập họ tên vào ô nhập
+Step 4: Nhập số điện thoại chứa ký tự không phải số vào ô nhập
+Step 5: Nhấn nút "Gửi bình luận"
+Step 6: Kiểm tra thông báo hiển thị trên giao diện</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>"Số điện thoại chỉ bao gồm những số." xuất hiện trên màn hình</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="12" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>TC_006</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Không gửi được khi số điện thoại ít hơn 10 chữ số</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Nhấn vào liên kết để điều hướng tới trang chi tiết sản phẩm
+Step 2: Nhập nội dung bình luận vào ô nhập
+Step 3: Nhập họ tên vào ô nhập
+Step 4: Nhập số điện thoại có ít hơn 10 chữ số vào ô nhập
+Step 5: Nhấn nút "Gửi bình luận"
+Step 6: Kiểm tra thông báo hiển thị trên giao diện</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>"Số điện thoại phải có ít nhất 10 số." xuất hiện trên màn hình</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr"/>
+      <c r="G10" s="12" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="'Test report'!A1" display="Back to TestReport"/>
+    <hyperlink ref="B1" location="BugList!A1" display="To Buglist"/>
+  </hyperlinks>
+  <pageMargins left="0.7875" right="0.7875" top="1.052777777777778" bottom="1.052777777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" firstPageNumber="0" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
+  <cols>
+    <col width="12" customWidth="1" style="5" min="1" max="1"/>
+    <col width="40" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
+    <col width="30" customWidth="1" style="5" min="3" max="3"/>
+    <col width="45" customWidth="1" style="5" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" style="5" min="7" max="7"/>
+    <col width="15" customWidth="1" style="5" min="8" max="8"/>
+    <col width="25" customWidth="1" style="5" min="9" max="9"/>
+    <col width="9" customWidth="1" style="5" min="10" max="17"/>
+    <col width="9" customWidth="1" style="5" min="18" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="12.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Back to TestReport</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>To Buglist</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="2">
+        <f>"Pass: "&amp;COUNTIF(#REF!,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E1" s="3">
+        <f>"Untested: "&amp;COUNTIF(#REF!,"Untest")</f>
+        <v/>
+      </c>
+      <c r="F1" s="3">
+        <f>"Untested: "&amp;COUNTIF(#REF!,"Untest")</f>
+        <v/>
+      </c>
+      <c r="G1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="12.75" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Module Code</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>DatHangNhanh</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="2">
+        <f>"Fail: "&amp;COUNTIF(#REF!,"Fail")</f>
+        <v/>
+      </c>
+      <c r="E2" s="3">
+        <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F2" s="3">
+        <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="12.75" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Lê Thị Ánh</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="2">
+        <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$973)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
+        <v/>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Number of cases: 4</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Number of cases: 4</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="n"/>
+    </row>
+    <row r="4" ht="28.35" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Test Case Description</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Pre -Condition</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Test Case Procedure</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Expected Output</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Actual Output</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Test date</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customFormat="1" customHeight="1" s="14">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Đặt hàng nhanh thành công</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập số điện thoại hợp lệ
+Step 3: Nhấn nút "Gửi"
+Step 4: Kiểm tra thông báo hiển thị</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Hệ thống kiểm tra dữ liệu nhập thành công và gửi thông tin đặt hàng nhanh
+Hiển thị thông báo có chứa “Cảm ơn bạn đã đặt hàng, vui lòng check lại đơn hàng trong messenger.”</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Số điện thoại rỗng</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Không nhập số điện thoại
+Step 3: Nhấn nút "Gửi"
+Step 4: Kiểm tra thông báo hiển thị</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Hệ thống hiển thị thông báo "Bạn chưa nhập số điện thoại."</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>TC_003</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Số điện thoại chứa ký tự không phải số</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập số điện thoại có ký tự không phải số
+Step 3: Nhấn nút "Gửi"
+Step 4: Kiểm tra thông báo hiển thị</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Hệ thống hiển thị thông báo "Số điện thoại chỉ bao gồm những số."</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>TC_004</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Số điện thoại ít hơn 10 chữ số</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập số điện thoại có ít hơn 10 chữ số
+Step 3: Nhấn nút "Gửi"
+Step 4: Kiểm tra thông báo hiển thị</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Hệ thống hiển thị thông báo "Số điện thoại phải có ít nhất 10 số."</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="12" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="60" customHeight="1"/>
+    <row r="10" ht="60" customHeight="1"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="'Test report'!A1" display="Back to TestReport"/>
+    <hyperlink ref="B1" location="BugList!A1" display="To Buglist"/>
+  </hyperlinks>
+  <pageMargins left="0.7875" right="0.7875" top="1.052777777777778" bottom="1.052777777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" firstPageNumber="0" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
+  <cols>
+    <col width="12" customWidth="1" style="5" min="1" max="1"/>
+    <col width="40" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
+    <col width="30" customWidth="1" style="5" min="3" max="3"/>
+    <col width="45" customWidth="1" style="5" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" style="5" min="7" max="7"/>
+    <col width="15" customWidth="1" style="5" min="8" max="8"/>
+    <col width="25" customWidth="1" style="5" min="9" max="9"/>
+    <col width="9" customWidth="1" style="5" min="10" max="17"/>
+    <col width="9" customWidth="1" style="5" min="18" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="12.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Back to TestReport</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>To Buglist</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="2">
+        <f>"Pass: "&amp;COUNTIF(#REF!,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E1" s="3">
+        <f>"Untested: "&amp;COUNTIF(#REF!,"Untest")</f>
+        <v/>
+      </c>
+      <c r="F1" s="3">
+        <f>"Untested: "&amp;COUNTIF(#REF!,"Untest")</f>
+        <v/>
+      </c>
+      <c r="G1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="12.75" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Module Code</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>MuaHang</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="2">
+        <f>"Fail: "&amp;COUNTIF(#REF!,"Fail")</f>
+        <v/>
+      </c>
+      <c r="E2" s="3">
+        <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F2" s="3">
+        <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="12.75" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Lê Thị Ánh</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="2">
+        <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$973)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
+        <v/>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Number of cases: 6</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Number of cases: 6</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="n"/>
+    </row>
+    <row r="4" ht="28.35" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Test Case Description</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Pre -Condition</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Test Case Procedure</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Expected Output</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Actual Output</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Test date</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="105" customFormat="1" customHeight="1" s="14">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Mua hàng thành công khi tất cả thông tin hợp lệ</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập họ và tên người mua vào ô nhập
+Step 3: Nhập số điện thoại vào ô nhập
+Step 4: Nhập địa chỉ nhận hàng vào ô nhập
+Step 5: Nhập yêu cầu thêm (nếu có) vào ô nhập
+Step 6: Nhấn nút "Mua hàng"
+Step 7: Kiểm tra thông báo hiển thị</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Hệ thống kiểm tra dữ liệu nhập thành công và gửi thông tin đơn hàng
+Hiển thị thông báo có chứa “Cảm ơn bạn đã đặt hàng, vui lòng check lại đơn hàng trong messenger.”</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Không nhập họ và tên người mua</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
+Step 2: Không nhập họ và tên người mua
+Step 3: Nhập số điện thoại vào ô nhập
+Step 4: Nhập địa chỉ nhận hàng vào ô nhập
+Step 5: Nhấn nút "Mua hàng"
+Step 6: Kiểm tra thông báo hiển thị</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Hệ thống hiển thị thông báo "Bạn chưa nhập họ và tên người mua."</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>TC_003</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Không nhập số điện thoại</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập họ và tên người mua vào ô nhập
+Step 3: Không nhập số điện thoại
+Step 4: Nhập địa chỉ nhận hàng vào ô nhập
+Step 5: Nhấn nút "Mua hàng"
+Step 6: Kiểm tra thông báo hiển thị</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Hệ thống hiển thị thông báo "Bạn chưa nhập số điện thoại."</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n"/>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>TC_004</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Nhập số điện thoại chứa ký tự không phải số</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập họ và tên người mua vào ô nhập
+Step 3: Nhập số điện thoại chứa ký tự không phải số vào ô nhập
+Step 4: Nhập địa chỉ nhận hàng vào ô nhập
+Step 5: Nhấn nút "Mua hàng"
+Step 6: Kiểm tra thông báo hiển thị</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Hệ thống hiển thị thông báo "Số điện thoại chỉ bao gồm những số."</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="12" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>TC_005</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Nhập số điện thoại ít hơn 10 chữ số</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập họ và tên người mua vào ô nhập
+Step 3: Nhập số điện thoại có ít hơn 10 chữ số vào ô nhập
+Step 4: Nhập địa chỉ nhận hàng vào ô nhập
+Step 5: Nhấn nút "Mua hàng"
+Step 6: Kiểm tra thông báo hiển thị</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Hệ thống hiển thị thông báo "Số điện thoại phải có ít nhất 10 số."</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="12" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>TC_006</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Không nhập địa chỉ nhận hàng</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Người dùng đang ở trang chủ</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập họ và tên người mua vào ô nhập
+Step 3: Nhập số điện thoại vào ô nhập
+Step 4: Không nhập địa chỉ nhận hàng
+Step 5: Nhấn nút "Mua hàng"
+Step 6: Kiểm tra thông báo hiển thị</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Hệ thống hiển thị thông báo "Bạn chưa nhập địa chỉ nhận hàng."</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr"/>
+      <c r="G10" s="12" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="'Test report'!A1" display="Back to TestReport"/>
+    <hyperlink ref="B1" location="BugList!A1" display="To Buglist"/>
+  </hyperlinks>
+  <pageMargins left="0.7875" right="0.7875" top="1.052777777777778" bottom="1.052777777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" firstPageNumber="0" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
 </file>
--- a/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
@@ -1701,7 +1701,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="105" customFormat="1" customHeight="1" s="14">
+    <row r="5" ht="120" customFormat="1" customHeight="1" s="14">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>TC_001</t>
@@ -1719,26 +1719,27 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
-Step 2: Nhập họ và tên người mua vào ô nhập
-Step 3: Nhập số điện thoại vào ô nhập
-Step 4: Nhập địa chỉ nhận hàng vào ô nhập
-Step 5: Nhập yêu cầu thêm (nếu có) vào ô nhập
-Step 6: Nhấn nút "Mua hàng"
-Step 7: Kiểm tra thông báo hiển thị</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhấn nút "Mua hàng"
+Step 3: Nhập họ và tên người mua
+Step 4: Nhập số điện thoại
+Step 5: Nhập địa chỉ nhận hàng
+Step 6: Nhập yêu cầu thêm (nếu có)
+Step 7: Nhấn nút "Mua"
+Step 8: Kiểm tra dữ liệu nhập</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống kiểm tra dữ liệu nhập thành công và gửi thông tin đơn hàng
-Hiển thị thông báo có chứa “Cảm ơn bạn đã đặt hàng, vui lòng check lại đơn hàng trong messenger.”</t>
+          <t>Hệ thống gửi thông tin đơn hàng
+Hiển thị thông báo chứa “Cảm ơn bạn đã đặt hàng, vui lòng check lại đơn hàng trong messenger.”</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
@@ -1761,12 +1762,12 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
-Step 2: Không nhập họ và tên người mua
-Step 3: Nhập số điện thoại vào ô nhập
-Step 4: Nhập địa chỉ nhận hàng vào ô nhập
-Step 5: Nhấn nút "Mua hàng"
-Step 6: Kiểm tra thông báo hiển thị</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhấn nút "Mua hàng"
+Step 3: Không nhập họ và tên người mua
+Step 4: Nhập số điện thoại
+Step 5: Nhập địa chỉ nhận hàng
+Step 6: Nhấn nút "Mua"</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -1778,7 +1779,7 @@
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
@@ -1801,12 +1802,12 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
-Step 2: Nhập họ và tên người mua vào ô nhập
-Step 3: Không nhập số điện thoại
-Step 4: Nhập địa chỉ nhận hàng vào ô nhập
-Step 5: Nhấn nút "Mua hàng"
-Step 6: Kiểm tra thông báo hiển thị</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhấn nút "Mua hàng"
+Step 3: Nhập họ và tên người mua
+Step 4: Không nhập số điện thoại
+Step 5: Nhập địa chỉ nhận hàng
+Step 6: Nhấn nút "Mua"</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -1818,7 +1819,7 @@
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
@@ -1831,7 +1832,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Nhập số điện thoại chứa ký tự không phải số</t>
+          <t>Số điện thoại chứa ký tự không phải số</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -1841,12 +1842,12 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
-Step 2: Nhập họ và tên người mua vào ô nhập
-Step 3: Nhập số điện thoại chứa ký tự không phải số vào ô nhập
-Step 4: Nhập địa chỉ nhận hàng vào ô nhập
-Step 5: Nhấn nút "Mua hàng"
-Step 6: Kiểm tra thông báo hiển thị</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhấn nút "Mua hàng"
+Step 3: Nhập họ và tên người mua
+Step 4: Nhập số điện thoại chứa ký tự không phải số
+Step 5: Nhập địa chỉ nhận hàng
+Step 6: Nhấn nút "Mua"</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -1858,7 +1859,7 @@
       <c r="G8" s="12" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr"/>
@@ -1871,7 +1872,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Nhập số điện thoại ít hơn 10 chữ số</t>
+          <t>Số điện thoại ít hơn 10 chữ số</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -1881,12 +1882,12 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
-Step 2: Nhập họ và tên người mua vào ô nhập
-Step 3: Nhập số điện thoại có ít hơn 10 chữ số vào ô nhập
-Step 4: Nhập địa chỉ nhận hàng vào ô nhập
-Step 5: Nhấn nút "Mua hàng"
-Step 6: Kiểm tra thông báo hiển thị</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhấn nút "Mua hàng"
+Step 3: Nhập họ và tên người mua
+Step 4: Nhập số điện thoại có ít hơn 10 chữ số
+Step 5: Nhập địa chỉ nhận hàng
+Step 6: Nhấn nút "Mua"</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -1898,7 +1899,7 @@
       <c r="G9" s="12" t="inlineStr"/>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr"/>
@@ -1921,12 +1922,12 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
-Step 2: Nhập họ và tên người mua vào ô nhập
-Step 3: Nhập số điện thoại vào ô nhập
-Step 4: Không nhập địa chỉ nhận hàng
-Step 5: Nhấn nút "Mua hàng"
-Step 6: Kiểm tra thông báo hiển thị</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhấn nút "Mua hàng"
+Step 3: Nhập họ và tên người mua
+Step 4: Nhập số điện thoại
+Step 5: Không nhập địa chỉ nhận hàng
+Step 6: Nhấn nút "Mua"</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -1938,7 +1939,7 @@
       <c r="G10" s="12" t="inlineStr"/>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr"/>

--- a/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/Sample_TestCase.xlsx
@@ -715,31 +715,31 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Tìm kiếm sản phẩm với từ khóa hợp lệ</t>
+          <t>Kiểm thử chức năng tìm kiếm khi nhập từ khóa hợp lệ.</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Hệ thống hiển thị trang cửa hàng.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhập từ khóa tìm kiếm vào ô tìm kiếm
-Step 2: Nhấn nút "Tìm kiếm"
-Step 3: Kiểm tra kết quả hiển thị danh sách sản phẩm phù hợp với từ khóa</t>
+          <t>Step 1: Người dùng nhập từ khóa tìm kiếm vào ô tìm kiếm.
+Step 2: Người dùng nhấn nút "Tìm kiếm".
+Step 3: Kiểm tra danh sách sản phẩm phù hợp với từ khóa đã hiển thị.</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Danh sách sản phẩm được hiển thị dựa trên từ khóa tìm kiếm</t>
+          <t>Hệ thống hiển thị danh sách các sản phẩm khớp với từ khóa tìm kiếm.</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
@@ -752,31 +752,31 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Tìm kiếm khi không nhập từ khóa</t>
+          <t>Kiểm thử chức năng tìm kiếm khi người dùng không nhập từ khóa.</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Hệ thống hiển thị trang cửa hàng.</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Không nhập dữ liệu vào ô tìm kiếm
-Step 2: Nhấn nút "Tìm kiếm"
-Step 3: Kiểm tra kết quả hiển thị danh sách tất cả sản phẩm trong cửa hàng</t>
+          <t>Step 1: Người dùng không nhập bất kỳ ký tự nào vào ô tìm kiếm.
+Step 2: Người dùng nhấn nút "Tìm kiếm".
+Step 3: Kiểm tra danh sách toàn bộ sản phẩm trong cửa hàng được hiển thị.</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Danh sách toàn bộ sản phẩm được hiển thị</t>
+          <t>Hệ thống hiển thị toàn bộ danh sách sản phẩm có sẵn trong cửa hàng.</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
@@ -789,31 +789,31 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Tìm kiếm khi không tìm thấy sản phẩm phù hợp</t>
+          <t>Kiểm thử chức năng tìm kiếm khi không có sản phẩm phù hợp.</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Hệ thống hiển thị trang cửa hàng.</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhập từ khóa chưa tồn tại trong kho hàng vào ô tìm kiếm
-Step 2: Nhấn nút "Tìm kiếm"
-Step 3: Kiểm tra thông báo hiển thị "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn."</t>
+          <t>Step 1: Người dùng nhập từ khóa tìm kiếm vào ô tìm kiếm.
+Step 2: Người dùng nhấn nút "Tìm kiếm".
+Step 3: Kiểm tra thông báo "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn.".</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>"Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn." được hiển thị trên giao diện</t>
+          <t>"Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn."</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
@@ -996,34 +996,34 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Thêm bình luận thành công trên trang chi tiết sản phẩm</t>
+          <t>Kiểm tra gửi bình luận thành công khi nhập đầy đủ thông tin.</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Hệ thống đang mở trang chi tiết sản phẩm.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhấn vào liên kết để điều hướng tới trang chi tiết sản phẩm
-Step 2: Nhập nội dung bình luận vào ô nhập
-Step 3: Nhập họ tên vào ô nhập
-Step 4: Nhập số điện thoại vào ô nhập
-Step 5: Nhấn nút "Gửi bình luận"
-Step 6: Kiểm tra thông báo hiển thị trên giao diện</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm.
+Step 2: Nhập nội dung bình luận vào ô "Bình luận".
+Step 3: Nhập họ tên vào ô "Họ và tên".
+Step 4: Nhập số điện thoại hợp lệ vào ô "Số điện thoại".
+Step 5: Nhấn nút "Gửi bình luận".
+Step 6: Kiểm tra thông báo "Gửi bình luận thành công." hiển thị.</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>"Gửi bình luận thành công." xuất hiện trên màn hình</t>
+          <t>"Gửi bình luận thành công." được hiển thị trên giao diện.</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
@@ -1036,34 +1036,34 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Không gửi được khi nội dung bình luận rỗng</t>
+          <t>Kiểm tra thông báo khi không nhập nội dung bình luận.</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Hệ thống đang mở trang chi tiết sản phẩm.</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhấn vào liên kết để điều hướng tới trang chi tiết sản phẩm
-Step 2: Không nhập nội dung bình luận
-Step 3: Nhập họ tên vào ô nhập
-Step 4: Nhập số điện thoại vào ô nhập
-Step 5: Nhấn nút "Gửi bình luận"
-Step 6: Kiểm tra thông báo hiển thị trên giao diện</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm.
+Step 2: Không nhập nội dung bình luận vào ô "Bình luận".
+Step 3: Nhập họ tên vào ô "Họ và tên".
+Step 4: Nhập số điện thoại hợp lệ vào ô "Số điện thoại".
+Step 5: Nhấn nút "Gửi bình luận".
+Step 6: Kiểm tra thông báo "Bạn chưa nhập bình luận." hiển thị.</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>"Bạn chưa nhập bình luận." xuất hiện trên màn hình</t>
+          <t>"Bạn chưa nhập bình luận." được hiển thị trên giao diện.</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
@@ -1076,34 +1076,34 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Không gửi được khi họ tên rỗng</t>
+          <t>Kiểm tra thông báo khi không nhập họ tên.</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Hệ thống đang mở trang chi tiết sản phẩm.</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhấn vào liên kết để điều hướng tới trang chi tiết sản phẩm
-Step 2: Nhập nội dung bình luận vào ô nhập
-Step 3: Không nhập họ tên
-Step 4: Nhập số điện thoại vào ô nhập
-Step 5: Nhấn nút "Gửi bình luận"
-Step 6: Kiểm tra thông báo hiển thị trên giao diện</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm.
+Step 2: Nhập nội dung bình luận vào ô "Bình luận".
+Step 3: Không nhập họ tên vào ô "Họ và tên".
+Step 4: Nhập số điện thoại hợp lệ vào ô "Số điện thoại".
+Step 5: Nhấn nút "Gửi bình luận".
+Step 6: Kiểm tra thông báo "Bạn chưa nhập tên." hiển thị.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>"Bạn chưa nhập tên." xuất hiện trên màn hình</t>
+          <t>"Bạn chưa nhập tên." được hiển thị trên giao diện.</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
@@ -1116,34 +1116,34 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Không gửi được khi số điện thoại rỗng</t>
+          <t>Kiểm tra thông báo khi không nhập số điện thoại.</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Hệ thống đang mở trang chi tiết sản phẩm.</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhấn vào liên kết để điều hướng tới trang chi tiết sản phẩm
-Step 2: Nhập nội dung bình luận vào ô nhập
-Step 3: Nhập họ tên vào ô nhập
-Step 4: Không nhập số điện thoại
-Step 5: Nhấn nút "Gửi bình luận"
-Step 6: Kiểm tra thông báo hiển thị trên giao diện</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm.
+Step 2: Nhập nội dung bình luận vào ô "Bình luận".
+Step 3: Nhập họ tên vào ô "Họ và tên".
+Step 4: Không nhập số điện thoại vào ô "Số điện thoại".
+Step 5: Nhấn nút "Gửi bình luận".
+Step 6: Kiểm tra thông báo "Bạn chưa nhập số điện thoại." hiển thị.</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>"Bạn chưa nhập số điện thoại." xuất hiện trên màn hình</t>
+          <t>"Bạn chưa nhập số điện thoại." được hiển thị trên giao diện.</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr"/>
       <c r="G8" s="12" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr"/>
@@ -1156,34 +1156,34 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Không gửi được khi số điện thoại chứa ký tự không phải số</t>
+          <t>Kiểm tra thông báo khi nhập số điện thoại chứa ký tự không phải số.</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Hệ thống đang mở trang chi tiết sản phẩm.</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhấn vào liên kết để điều hướng tới trang chi tiết sản phẩm
-Step 2: Nhập nội dung bình luận vào ô nhập
-Step 3: Nhập họ tên vào ô nhập
-Step 4: Nhập số điện thoại chứa ký tự không phải số vào ô nhập
-Step 5: Nhấn nút "Gửi bình luận"
-Step 6: Kiểm tra thông báo hiển thị trên giao diện</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm.
+Step 2: Nhập nội dung bình luận vào ô "Bình luận".
+Step 3: Nhập họ tên vào ô "Họ và tên".
+Step 4: Nhập số điện thoại chứa ký tự không phải số vào ô "Số điện thoại".
+Step 5: Nhấn nút "Gửi bình luận".
+Step 6: Kiểm tra thông báo "Số điện thoại chỉ bao gồm những số." hiển thị.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>"Số điện thoại chỉ bao gồm những số." xuất hiện trên màn hình</t>
+          <t>"Số điện thoại chỉ bao gồm những số." được hiển thị trên giao diện.</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr"/>
       <c r="G9" s="12" t="inlineStr"/>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr"/>
@@ -1196,34 +1196,34 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Không gửi được khi số điện thoại ít hơn 10 chữ số</t>
+          <t>Kiểm tra thông báo khi nhập số điện thoại ít hơn 10 chữ số.</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Hệ thống đang mở trang chi tiết sản phẩm.</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Nhấn vào liên kết để điều hướng tới trang chi tiết sản phẩm
-Step 2: Nhập nội dung bình luận vào ô nhập
-Step 3: Nhập họ tên vào ô nhập
-Step 4: Nhập số điện thoại có ít hơn 10 chữ số vào ô nhập
-Step 5: Nhấn nút "Gửi bình luận"
-Step 6: Kiểm tra thông báo hiển thị trên giao diện</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm.
+Step 2: Nhập nội dung bình luận vào ô "Bình luận".
+Step 3: Nhập họ tên vào ô "Họ và tên".
+Step 4: Nhập số điện thoại có ít hơn 10 chữ số vào ô "Số điện thoại".
+Step 5: Nhấn nút "Gửi bình luận".
+Step 6: Kiểm tra thông báo "Số điện thoại phải có ít nhất 10 số." hiển thị.</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>"Số điện thoại phải có ít nhất 10 số." xuất hiện trên màn hình</t>
+          <t>"Số điện thoại phải có ít nhất 10 số." được hiển thị trên giao diện.</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr"/>
       <c r="G10" s="12" t="inlineStr"/>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr"/>
@@ -1395,33 +1395,32 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Đặt hàng nhanh thành công</t>
+          <t>Kiểm tra chức năng đặt hàng nhanh với số điện thoại hợp lệ.</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Hệ thống đang mở trang chủ và đã đăng nhập thành công (nếu cần).</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Step 1: Truy cập vào trang chi tiết sản phẩm
-Step 2: Nhập số điện thoại hợp lệ
+Step 2: Nhập số điện thoại hợp lệ vào ô số điện thoại
 Step 3: Nhấn nút "Gửi"
-Step 4: Kiểm tra thông báo hiển thị</t>
+Step 4: Kiểm tra thông báo "Cảm ơn bạn đã đặt hàng, vui lòng check lại đơn hàng trong messenger." hiển thị</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống kiểm tra dữ liệu nhập thành công và gửi thông tin đặt hàng nhanh
-Hiển thị thông báo có chứa “Cảm ơn bạn đã đặt hàng, vui lòng check lại đơn hàng trong messenger.”</t>
+          <t>"Cảm ơn bạn đã đặt hàng, vui lòng check lại đơn hàng trong messenger." được hiển thị trên giao diện.</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
@@ -1434,32 +1433,32 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Số điện thoại rỗng</t>
+          <t>Kiểm tra thông báo lỗi khi số điện thoại rỗng.</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Hệ thống đang online và trang chi tiết sản phẩm hiển thị.</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Step 1: Truy cập vào trang chi tiết sản phẩm
-Step 2: Không nhập số điện thoại
+Step 2: Không nhập dữ liệu vào ô số điện thoại
 Step 3: Nhấn nút "Gửi"
 Step 4: Kiểm tra thông báo hiển thị</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo "Bạn chưa nhập số điện thoại."</t>
+          <t>Thông báo "Bạn chưa nhập số điện thoại." hiển thị</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
@@ -1472,32 +1471,32 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Số điện thoại chứa ký tự không phải số</t>
+          <t>Kiểm tra thông báo lỗi khi số điện thoại chứa ký tự không phải số.</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Hệ thống đang online và trang chi tiết sản phẩm hiển thị.</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Step 1: Truy cập vào trang chi tiết sản phẩm
-Step 2: Nhập số điện thoại có ký tự không phải số
+Step 2: Nhập số điện thoại có chứa ký tự không phải số vào ô số điện thoại
 Step 3: Nhấn nút "Gửi"
 Step 4: Kiểm tra thông báo hiển thị</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo "Số điện thoại chỉ bao gồm những số."</t>
+          <t>Thông báo "Số điện thoại chỉ bao gồm những số." hiển thị</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
@@ -1510,32 +1509,32 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Số điện thoại ít hơn 10 chữ số</t>
+          <t>Kiểm tra thông báo lỗi khi số điện thoại ít hơn 10 chữ số.</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Hệ thống đang online và trang chi tiết sản phẩm hiển thị.</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Step 1: Truy cập vào trang chi tiết sản phẩm
-Step 2: Nhập số điện thoại có ít hơn 10 chữ số
+Step 2: Nhập số điện thoại có ít hơn 10 chữ số vào ô số điện thoại
 Step 3: Nhấn nút "Gửi"
 Step 4: Kiểm tra thông báo hiển thị</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo "Số điện thoại phải có ít nhất 10 số."</t>
+          <t>Thông báo "Số điện thoại phải có ít nhất 10 số." hiển thị</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr"/>
       <c r="G8" s="12" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr"/>
